--- a/output/pdf_financials_xlsx/SLT.U.xlsx
+++ b/output/pdf_financials_xlsx/SLT.U.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>15.169758</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>6.041165</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>4.496709</v>
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.00012</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-15.169758</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-6.041165</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.785561</v>
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1.677634</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>2.639053</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1034,10 +1034,10 @@
         <v>-0.00012</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.492124</v>
+        <v>-15.169758</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.402112</v>
+        <v>-6.041165</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-46.889204</v>
@@ -1078,10 +1078,10 @@
         <v>-0.00012</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.492124</v>
+        <v>-15.169758</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.940807</v>
+        <v>-5.57986</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-46.373341</v>
@@ -1182,19 +1182,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.680325</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.648806</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.236079</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.104053</v>
       </c>
     </row>
     <row r="35">
@@ -1226,19 +1226,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.680325</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.648806</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.236079</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.104053</v>
       </c>
     </row>
     <row r="37">
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.958716</v>
+        <v>0.30991</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.679676</v>
+        <v>0.443597</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.239567</v>
+        <v>1.135514</v>
       </c>
     </row>
     <row r="49">
@@ -3194,10 +3194,10 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.415</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.479865</v>
       </c>
     </row>
     <row r="125">
@@ -3216,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.415</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.479865</v>
       </c>
     </row>
     <row r="126">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -9995,7 +9995,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -14368,7 +14372,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -14532,7 +14536,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15145,7 +15149,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">

--- a/output/pdf_financials_xlsx/SLT.U.xlsx
+++ b/output/pdf_financials_xlsx/SLT.U.xlsx
@@ -2928,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.052467</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.061804</v>
       </c>
     </row>
     <row r="113">
@@ -9509,7 +9509,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -10393,7 +10397,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SLT.U.xlsx
+++ b/output/pdf_financials_xlsx/SLT.U.xlsx
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.068175</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.144641</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>2.253919</v>
       </c>
     </row>
     <row r="41">
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>3.141425</v>
+        <v>3.2096</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>5.448835</v>
+        <v>5.593476</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>13.122449</v>
+        <v>15.376368</v>
       </c>
     </row>
     <row r="42">
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.30991</v>
+        <v>0.241735</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.443597</v>
+        <v>0.298956</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.135514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2815,13 +2815,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.043655</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.037263</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.198177</v>
       </c>
     </row>
     <row r="108">
@@ -3335,17 +3335,13 @@
         <v>1e-06</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.680325</v>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.725587</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.648806</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>1.236079</v>
       </c>
     </row>
     <row r="131">
@@ -3407,17 +3403,13 @@
         <v>0.680325</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.171885</v>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.648806</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>1.236079</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>5.104053</v>
       </c>
     </row>
     <row r="134">
@@ -4051,7 +4043,11 @@
           <t>Goodwill and intangible assets, net 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -5379,7 +5375,11 @@
           <t>Goodwill and intangible assets, net 10</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -8834,7 +8834,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -10206,7 +10210,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -10243,7 +10251,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
